--- a/exports/trend_1d/DLF_full_report.xlsx
+++ b/exports/trend_1d/DLF_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:U80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>15.75</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42051</v>
+        <v>42053</v>
       </c>
       <c r="H2" t="n">
-        <v>155.5</v>
+        <v>149.94</v>
       </c>
       <c r="I2" t="n">
         <v>150.4787084088741</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" t="n">
-        <v>5.21</v>
+        <v>1.45</v>
       </c>
       <c r="L2" t="n">
         <v>7.61</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42076</v>
+        <v>42079</v>
       </c>
       <c r="H3" t="n">
-        <v>157.4</v>
+        <v>164.3</v>
       </c>
       <c r="I3" t="n">
         <v>163.2839622308416</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.98</v>
+        <v>-9.58</v>
       </c>
       <c r="L3" t="n">
-        <v>8.5</v>
+        <v>10.24</v>
       </c>
       <c r="M3" t="n">
         <v>3.27</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>15.56</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>146.25</v>
+        <v>138.9</v>
       </c>
       <c r="I4" t="n">
         <v>144.9646067480793</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.99</v>
+        <v>-15.46</v>
       </c>
       <c r="L4" t="n">
-        <v>12.57</v>
+        <v>15.95</v>
       </c>
       <c r="M4" t="n">
         <v>2.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.48</v>
+        <v>5.03</v>
       </c>
       <c r="O4" t="n">
         <v>4.38</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42215</v>
+        <v>42216</v>
       </c>
       <c r="H5" t="n">
-        <v>109.7</v>
+        <v>115.05</v>
       </c>
       <c r="I5" t="n">
         <v>111.0895135066351</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K5" t="n">
-        <v>21.02</v>
+        <v>17.17</v>
       </c>
       <c r="L5" t="n">
         <v>6.26</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>16.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>113.95</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>108.7543815353873</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.96</v>
+        <v>-15.99</v>
       </c>
       <c r="L6" t="n">
-        <v>6.08</v>
+        <v>18.86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.08</v>
+        <v>7.85</v>
       </c>
       <c r="N6" t="n">
-        <v>5.83</v>
+        <v>15.18</v>
       </c>
       <c r="O6" t="n">
         <v>4.88</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>34.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42275</v>
+        <v>42276</v>
       </c>
       <c r="H7" t="n">
-        <v>129.55</v>
+        <v>134.6</v>
       </c>
       <c r="I7" t="n">
         <v>130.0228042419339</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>-34.04</v>
+        <v>-39.27</v>
       </c>
       <c r="L7" t="n">
-        <v>38.39</v>
+        <v>42.06</v>
       </c>
       <c r="M7" t="n">
         <v>4.43</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>18.69</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42305</v>
+        <v>42306</v>
       </c>
       <c r="H8" t="n">
-        <v>123.9</v>
+        <v>120.4</v>
       </c>
       <c r="I8" t="n">
         <v>122.4203120703675</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.95</v>
+        <v>-10.55</v>
       </c>
       <c r="L8" t="n">
-        <v>8.880000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="M8" t="n">
         <v>3.38</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42338</v>
+        <v>42339</v>
       </c>
       <c r="H9" t="n">
-        <v>114.6</v>
+        <v>117.9</v>
       </c>
       <c r="I9" t="n">
         <v>117.111949157048</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>2.08</v>
       </c>
       <c r="L9" t="n">
         <v>4.4</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>13.03</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H10" t="n">
-        <v>114.75</v>
+        <v>106.8</v>
       </c>
       <c r="I10" t="n">
         <v>108.0832599480382</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.67</v>
+        <v>-9.41</v>
       </c>
       <c r="L10" t="n">
         <v>10.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="N10" t="n">
-        <v>5.32</v>
+        <v>6.93</v>
       </c>
       <c r="O10" t="n">
         <v>2.88</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>15.16</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42429</v>
+        <v>42430</v>
       </c>
       <c r="H11" t="n">
-        <v>88.95</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>94.84614609156893</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" t="n">
-        <v>16.71</v>
+        <v>8.15</v>
       </c>
       <c r="L11" t="n">
         <v>6.74</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>21.48</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42613</v>
+        <v>42614</v>
       </c>
       <c r="H12" t="n">
-        <v>154.85</v>
+        <v>148.75</v>
       </c>
       <c r="I12" t="n">
         <v>152.1576773575244</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K12" t="n">
-        <v>57.85</v>
+        <v>51.63</v>
       </c>
       <c r="L12" t="n">
         <v>9.17</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.23</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H13" t="n">
-        <v>119.05</v>
+        <v>125.5</v>
       </c>
       <c r="I13" t="n">
         <v>119.4509932388757</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K13" t="n">
-        <v>19.97</v>
+        <v>15.63</v>
       </c>
       <c r="L13" t="n">
         <v>7.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H14" t="n">
-        <v>197.1</v>
+        <v>190.35</v>
       </c>
       <c r="I14" t="n">
         <v>190.8462955322049</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K14" t="n">
-        <v>57.05</v>
+        <v>51.67</v>
       </c>
       <c r="L14" t="n">
         <v>5.14</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42921</v>
+        <v>42922</v>
       </c>
       <c r="H15" t="n">
-        <v>197.4</v>
+        <v>201.15</v>
       </c>
       <c r="I15" t="n">
         <v>198.7657196167935</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.7</v>
+        <v>-5.67</v>
       </c>
       <c r="L15" t="n">
-        <v>7.07</v>
+        <v>7.12</v>
       </c>
       <c r="M15" t="n">
         <v>1.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H16" t="n">
-        <v>191.35</v>
+        <v>178.6</v>
       </c>
       <c r="I16" t="n">
         <v>188.5519104015537</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.87</v>
+        <v>-11.21</v>
       </c>
       <c r="L16" t="n">
-        <v>6.74</v>
+        <v>12.13</v>
       </c>
       <c r="M16" t="n">
         <v>0.92</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>6.66</v>
       </c>
       <c r="O16" t="n">
         <v>1.9</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>13.79</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42969</v>
+        <v>42970</v>
       </c>
       <c r="H17" t="n">
-        <v>175.3</v>
+        <v>185.95</v>
       </c>
       <c r="I17" t="n">
         <v>185.8590681295957</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.85</v>
+        <v>-4.12</v>
       </c>
       <c r="L17" t="n">
         <v>7.78</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.34</v>
       </c>
       <c r="N17" t="n">
         <v>16.78</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>18.12</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H18" t="n">
-        <v>185.05</v>
+        <v>173.5</v>
       </c>
       <c r="I18" t="n">
         <v>175.2173400336414</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.48</v>
+        <v>-6.7</v>
       </c>
       <c r="L18" t="n">
-        <v>5.19</v>
+        <v>7.56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="N18" t="n">
-        <v>3.66</v>
+        <v>6.24</v>
       </c>
       <c r="O18" t="n">
         <v>6.08</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>14.05</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H19" t="n">
-        <v>182.05</v>
+        <v>184.35</v>
       </c>
       <c r="I19" t="n">
         <v>183.0257162015971</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.93</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" t="n">
-        <v>6.25</v>
+        <v>8.07</v>
       </c>
       <c r="M19" t="n">
         <v>2.37</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H20" t="n">
-        <v>250.1</v>
+        <v>245</v>
       </c>
       <c r="I20" t="n">
         <v>245.9036835665913</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>35.67</v>
+        <v>32.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.25</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="H21" t="n">
-        <v>188.9</v>
+        <v>196.3</v>
       </c>
       <c r="I21" t="n">
         <v>191.3927869474941</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K21" t="n">
-        <v>22.9</v>
+        <v>19.88</v>
       </c>
       <c r="L21" t="n">
         <v>3.55</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>13.27</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H22" t="n">
-        <v>199.55</v>
+        <v>185.1</v>
       </c>
       <c r="I22" t="n">
         <v>197.502548707369</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K22" t="n">
-        <v>1.66</v>
+        <v>-5.71</v>
       </c>
       <c r="L22" t="n">
-        <v>6.24</v>
+        <v>7.26</v>
       </c>
       <c r="M22" t="n">
         <v>3.49</v>
       </c>
       <c r="N22" t="n">
-        <v>4.99</v>
+        <v>7.24</v>
       </c>
       <c r="O22" t="n">
         <v>3.92</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>20.2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43424</v>
+        <v>43425</v>
       </c>
       <c r="H23" t="n">
-        <v>174.9</v>
+        <v>182.8</v>
       </c>
       <c r="I23" t="n">
         <v>180.1047361483243</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23" t="n">
-        <v>5.51</v>
+        <v>1.24</v>
       </c>
       <c r="L23" t="n">
         <v>7.97</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>15.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H24" t="n">
-        <v>177.75</v>
+        <v>158</v>
       </c>
       <c r="I24" t="n">
         <v>167.1372914908032</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.76</v>
+        <v>-13.57</v>
       </c>
       <c r="L24" t="n">
-        <v>10.83</v>
+        <v>21.72</v>
       </c>
       <c r="M24" t="n">
         <v>1.68</v>
       </c>
       <c r="N24" t="n">
-        <v>5.42</v>
+        <v>11.11</v>
       </c>
       <c r="O24" t="n">
         <v>4.52</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>19.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H25" t="n">
-        <v>176.85</v>
+        <v>187.75</v>
       </c>
       <c r="I25" t="n">
         <v>181.8951068793043</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.93</v>
+        <v>-18.83</v>
       </c>
       <c r="L25" t="n">
-        <v>14.59</v>
+        <v>19.43</v>
       </c>
       <c r="M25" t="n">
         <v>1.27</v>
       </c>
       <c r="N25" t="n">
-        <v>4.99</v>
+        <v>6.16</v>
       </c>
       <c r="O25" t="n">
         <v>-11.11</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>13.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43565</v>
+        <v>43566</v>
       </c>
       <c r="H26" t="n">
-        <v>180.1</v>
+        <v>177.7</v>
       </c>
       <c r="I26" t="n">
         <v>178.4891453550348</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.07</v>
+        <v>-5.35</v>
       </c>
       <c r="L26" t="n">
-        <v>5.41</v>
+        <v>6.36</v>
       </c>
       <c r="M26" t="n">
         <v>0.87</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43607</v>
+        <v>43608</v>
       </c>
       <c r="H27" t="n">
-        <v>173.9</v>
+        <v>180.7</v>
       </c>
       <c r="I27" t="n">
         <v>180.6264582110364</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>2.14</v>
+        <v>-1.69</v>
       </c>
       <c r="L27" t="n">
         <v>5.74</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H28" t="n">
-        <v>177.85</v>
+        <v>172.65</v>
       </c>
       <c r="I28" t="n">
         <v>174.6245890571063</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.58</v>
+        <v>-4.45</v>
       </c>
       <c r="L28" t="n">
-        <v>3.71</v>
+        <v>5.73</v>
       </c>
       <c r="M28" t="n">
         <v>0.65</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.43</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43756</v>
+        <v>43760</v>
       </c>
       <c r="H29" t="n">
-        <v>168.85</v>
+        <v>178.2</v>
       </c>
       <c r="I29" t="n">
         <v>171.4296814621302</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>-3.21</v>
       </c>
       <c r="L29" t="n">
         <v>14.05</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.57</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H30" t="n">
-        <v>260.45</v>
+        <v>228.9</v>
       </c>
       <c r="I30" t="n">
         <v>244.6613660349666</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K30" t="n">
-        <v>46.16</v>
+        <v>28.45</v>
       </c>
       <c r="L30" t="n">
         <v>4.97</v>
@@ -2151,7 +2510,7 @@
         <v>3.64</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>12.11</v>
       </c>
       <c r="O30" t="n">
         <v>5.54</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>20.47</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H31" t="n">
-        <v>152.2</v>
+        <v>157.2</v>
       </c>
       <c r="I31" t="n">
         <v>155.1983528857359</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K31" t="n">
-        <v>33.51</v>
+        <v>31.32</v>
       </c>
       <c r="L31" t="n">
         <v>16.45</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>16.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H32" t="n">
-        <v>139.9</v>
+        <v>137.1</v>
       </c>
       <c r="I32" t="n">
         <v>139.360609618501</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K32" t="n">
-        <v>-11.01</v>
+        <v>-12.79</v>
       </c>
       <c r="L32" t="n">
-        <v>11.39</v>
+        <v>13.17</v>
       </c>
       <c r="M32" t="n">
         <v>3.81</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>16.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44060</v>
+        <v>44061</v>
       </c>
       <c r="H33" t="n">
-        <v>147.15</v>
+        <v>157.15</v>
       </c>
       <c r="I33" t="n">
         <v>153.7901480137024</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.33</v>
+        <v>-14.62</v>
       </c>
       <c r="L33" t="n">
-        <v>9.699999999999999</v>
+        <v>16.96</v>
       </c>
       <c r="M33" t="n">
         <v>1.44</v>
       </c>
       <c r="N33" t="n">
-        <v>4.79</v>
+        <v>6.8</v>
       </c>
       <c r="O33" t="n">
         <v>-2</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.22</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H34" t="n">
-        <v>152.15</v>
+        <v>150.25</v>
       </c>
       <c r="I34" t="n">
         <v>151.9464067644015</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.18</v>
+        <v>-4.39</v>
       </c>
       <c r="L34" t="n">
         <v>6.71</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.47</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H35" t="n">
-        <v>167.45</v>
+        <v>172.1</v>
       </c>
       <c r="I35" t="n">
         <v>170.5591883824004</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.45</v>
+        <v>-14.54</v>
       </c>
       <c r="L35" t="n">
-        <v>12.61</v>
+        <v>15.94</v>
       </c>
       <c r="M35" t="n">
         <v>2.32</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>13.49</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44132</v>
+        <v>44133</v>
       </c>
       <c r="H36" t="n">
-        <v>156</v>
+        <v>153.1</v>
       </c>
       <c r="I36" t="n">
         <v>153.3246453313251</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.359999999999999</v>
+        <v>-11.04</v>
       </c>
       <c r="L36" t="n">
-        <v>9.82</v>
+        <v>12.49</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="N36" t="n">
         <v>5.51</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H37" t="n">
-        <v>172.8</v>
+        <v>180.5</v>
       </c>
       <c r="I37" t="n">
         <v>173.1102251981176</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.87</v>
+        <v>-17.9</v>
       </c>
       <c r="L37" t="n">
-        <v>14.08</v>
+        <v>18.84</v>
       </c>
       <c r="M37" t="n">
         <v>1.38</v>
       </c>
       <c r="N37" t="n">
-        <v>4.11</v>
+        <v>4.46</v>
       </c>
       <c r="O37" t="n">
         <v>-1.86</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.39</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H38" t="n">
-        <v>297.95</v>
+        <v>284.15</v>
       </c>
       <c r="I38" t="n">
         <v>286.0948186401789</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K38" t="n">
-        <v>65.06999999999999</v>
+        <v>57.42</v>
       </c>
       <c r="L38" t="n">
         <v>4.71</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.09</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H39" t="n">
-        <v>268.4</v>
+        <v>277.05</v>
       </c>
       <c r="I39" t="n">
         <v>275.2216117871972</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K39" t="n">
-        <v>5.54</v>
+        <v>2.5</v>
       </c>
       <c r="L39" t="n">
         <v>4.66</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.93</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44376</v>
+        <v>44377</v>
       </c>
       <c r="H40" t="n">
-        <v>287.2</v>
+        <v>281.1</v>
       </c>
       <c r="I40" t="n">
         <v>281.3501945996109</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
-        <v>3.66</v>
+        <v>1.46</v>
       </c>
       <c r="L40" t="n">
         <v>3.41</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
       <c r="H41" t="n">
-        <v>310.95</v>
+        <v>314.2</v>
       </c>
       <c r="I41" t="n">
         <v>311.3849855543771</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.62</v>
+        <v>-11.78</v>
       </c>
       <c r="L41" t="n">
-        <v>11.35</v>
+        <v>13.38</v>
       </c>
       <c r="M41" t="n">
         <v>0.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.43</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H42" t="n">
-        <v>327.1</v>
+        <v>309</v>
       </c>
       <c r="I42" t="n">
         <v>320.1246104072537</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>4.11</v>
+        <v>-1.65</v>
       </c>
       <c r="L42" t="n">
-        <v>1.23</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>5.53</v>
       </c>
       <c r="O42" t="n">
         <v>1.05</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>13.85</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44441</v>
+        <v>44442</v>
       </c>
       <c r="H43" t="n">
-        <v>338.9</v>
+        <v>343.7</v>
       </c>
       <c r="I43" t="n">
         <v>342.8436389809643</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.68</v>
+        <v>-11.23</v>
       </c>
       <c r="L43" t="n">
-        <v>10.39</v>
+        <v>12.17</v>
       </c>
       <c r="M43" t="n">
         <v>1.59</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H44" t="n">
-        <v>407.25</v>
+        <v>376.85</v>
       </c>
       <c r="I44" t="n">
         <v>391.0312224226903</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K44" t="n">
-        <v>18.49</v>
+        <v>9.65</v>
       </c>
       <c r="L44" t="n">
         <v>7.03</v>
       </c>
       <c r="M44" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="N44" t="n">
-        <v>6.18</v>
+        <v>7.46</v>
       </c>
       <c r="O44" t="n">
         <v>1.42</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H45" t="n">
-        <v>417.35</v>
+        <v>423.8</v>
       </c>
       <c r="I45" t="n">
         <v>419.0195446972045</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.75</v>
+        <v>-12.46</v>
       </c>
       <c r="L45" t="n">
         <v>13.25</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>395.1</v>
+        <v>372</v>
       </c>
       <c r="I46" t="n">
         <v>383.0765168850849</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.77</v>
+        <v>-12.22</v>
       </c>
       <c r="L46" t="n">
-        <v>7.88</v>
+        <v>13.74</v>
       </c>
       <c r="M46" t="n">
         <v>1.23</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>5.85</v>
       </c>
       <c r="O46" t="n">
         <v>1.55</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.85</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44644</v>
+        <v>44645</v>
       </c>
       <c r="H47" t="n">
-        <v>356.6</v>
+        <v>365.1</v>
       </c>
       <c r="I47" t="n">
         <v>364.7356577784607</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" t="n">
-        <v>4.14</v>
+        <v>1.85</v>
       </c>
       <c r="L47" t="n">
         <v>10.15</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.63</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H48" t="n">
-        <v>379.7</v>
+        <v>364</v>
       </c>
       <c r="I48" t="n">
         <v>367.0543438426944</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>-0.3</v>
       </c>
       <c r="L48" t="n">
         <v>2.47</v>
@@ -3177,7 +3752,7 @@
         <v>1.39</v>
       </c>
       <c r="N48" t="n">
-        <v>2.84</v>
+        <v>4.13</v>
       </c>
       <c r="O48" t="n">
         <v>2.38</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.82</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H49" t="n">
-        <v>336.9</v>
+        <v>340.4</v>
       </c>
       <c r="I49" t="n">
         <v>339.3420629078181</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K49" t="n">
-        <v>7.45</v>
+        <v>6.48</v>
       </c>
       <c r="L49" t="n">
         <v>6.15</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.58</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H50" t="n">
-        <v>380.7</v>
+        <v>369.95</v>
       </c>
       <c r="I50" t="n">
         <v>378.2889602948924</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>11.84</v>
+        <v>8.68</v>
       </c>
       <c r="L50" t="n">
         <v>1.66</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.74</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H51" t="n">
-        <v>385.5</v>
+        <v>389.65</v>
       </c>
       <c r="I51" t="n">
         <v>388.3905414843601</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.2</v>
+        <v>-5.33</v>
       </c>
       <c r="L51" t="n">
-        <v>5.31</v>
+        <v>5.96</v>
       </c>
       <c r="M51" t="n">
         <v>1.77</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.97</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44914</v>
+        <v>44915</v>
       </c>
       <c r="H52" t="n">
-        <v>396.6</v>
+        <v>389.35</v>
       </c>
       <c r="I52" t="n">
         <v>389.3837419510972</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K52" t="n">
-        <v>1.78</v>
+        <v>-0.08</v>
       </c>
       <c r="L52" t="n">
         <v>2.48</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45001</v>
+        <v>45002</v>
       </c>
       <c r="H53" t="n">
-        <v>360.05</v>
+        <v>375.25</v>
       </c>
       <c r="I53" t="n">
         <v>369.2365933135936</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K53" t="n">
-        <v>7.53</v>
+        <v>3.62</v>
       </c>
       <c r="L53" t="n">
         <v>1.76</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H54" t="n">
-        <v>482</v>
+        <v>470.95</v>
       </c>
       <c r="I54" t="n">
         <v>476.7640499792356</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K54" t="n">
-        <v>28.45</v>
+        <v>25.5</v>
       </c>
       <c r="L54" t="n">
         <v>7.66</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.19</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45170</v>
+        <v>45173</v>
       </c>
       <c r="H55" t="n">
-        <v>503.25</v>
+        <v>513.9</v>
       </c>
       <c r="I55" t="n">
         <v>509.5261385131433</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.86</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>8.19</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>0.59</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H56" t="n">
-        <v>532.95</v>
+        <v>530.15</v>
       </c>
       <c r="I56" t="n">
         <v>531.2994252304311</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K56" t="n">
-        <v>3.71</v>
+        <v>3.16</v>
       </c>
       <c r="L56" t="n">
         <v>1.93</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>8.34</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H57" t="n">
-        <v>554.45</v>
+        <v>563.5</v>
       </c>
       <c r="I57" t="n">
         <v>563.1365943811144</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.58</v>
+        <v>-6.29</v>
       </c>
       <c r="L57" t="n">
-        <v>5.24</v>
+        <v>7.62</v>
       </c>
       <c r="M57" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="N57" t="n">
         <v>3.41</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H58" t="n">
-        <v>777.05</v>
+        <v>739.3</v>
       </c>
       <c r="I58" t="n">
         <v>748.7549888756341</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K58" t="n">
-        <v>37.9</v>
+        <v>31.2</v>
       </c>
       <c r="L58" t="n">
         <v>1.03</v>
@@ -3747,7 +4442,7 @@
         <v>0.87</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>4.86</v>
       </c>
       <c r="O58" t="n">
         <v>1.63</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>12.6</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="H59" t="n">
-        <v>797.35</v>
+        <v>827.45</v>
       </c>
       <c r="I59" t="n">
         <v>808.2458046837497</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.85</v>
+        <v>-11.92</v>
       </c>
       <c r="L59" t="n">
-        <v>9.390000000000001</v>
+        <v>13.39</v>
       </c>
       <c r="M59" t="n">
         <v>3.83</v>
       </c>
       <c r="N59" t="n">
-        <v>2.55</v>
+        <v>3.78</v>
       </c>
       <c r="O59" t="n">
         <v>-4.86</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.49</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="H60" t="n">
-        <v>911.25</v>
+        <v>864.4</v>
       </c>
       <c r="I60" t="n">
         <v>869.6180483215225</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>10.13</v>
+        <v>4.47</v>
       </c>
       <c r="L60" t="n">
         <v>3.43</v>
@@ -3861,7 +4580,7 @@
         <v>1.25</v>
       </c>
       <c r="N60" t="n">
-        <v>3.21</v>
+        <v>5.14</v>
       </c>
       <c r="O60" t="n">
         <v>3.78</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>11.22</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H61" t="n">
-        <v>897</v>
+        <v>948.25</v>
       </c>
       <c r="I61" t="n">
         <v>902.473757843125</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.77</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>5.89</v>
+        <v>11.94</v>
       </c>
       <c r="M61" t="n">
         <v>1.59</v>
       </c>
       <c r="N61" t="n">
-        <v>3.84</v>
+        <v>5.71</v>
       </c>
       <c r="O61" t="n">
         <v>-5.14</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H62" t="n">
-        <v>855.9</v>
+        <v>852.5</v>
       </c>
       <c r="I62" t="n">
         <v>854.0734728372826</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.74</v>
+        <v>-10.1</v>
       </c>
       <c r="L62" t="n">
         <v>12.05</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>10.12</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H63" t="n">
-        <v>879.9</v>
+        <v>889.15</v>
       </c>
       <c r="I63" t="n">
         <v>883.9123832125546</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.21</v>
+        <v>-4.3</v>
       </c>
       <c r="L63" t="n">
-        <v>4.15</v>
+        <v>4.58</v>
       </c>
       <c r="M63" t="n">
         <v>4.93</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H64" t="n">
-        <v>864.85</v>
+        <v>844.85</v>
       </c>
       <c r="I64" t="n">
         <v>848.3841863472411</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.73</v>
+        <v>-4.98</v>
       </c>
       <c r="L64" t="n">
         <v>9.98</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.08</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H65" t="n">
-        <v>822.95</v>
+        <v>849.1</v>
       </c>
       <c r="I65" t="n">
         <v>836.8488020325045</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K65" t="n">
-        <v>2.59</v>
+        <v>-0.5</v>
       </c>
       <c r="L65" t="n">
         <v>5.12</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.09</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H66" t="n">
-        <v>834.85</v>
+        <v>820.7</v>
       </c>
       <c r="I66" t="n">
         <v>821.3519759076073</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.68</v>
+        <v>-3.34</v>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>3.77</v>
       </c>
       <c r="M66" t="n">
         <v>1.31</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H67" t="n">
-        <v>695.9</v>
+        <v>706</v>
       </c>
       <c r="I67" t="n">
         <v>704.8005541509378</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K67" t="n">
-        <v>15.21</v>
+        <v>13.98</v>
       </c>
       <c r="L67" t="n">
         <v>2.33</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.02</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H68" t="n">
-        <v>653.95</v>
+        <v>608.05</v>
       </c>
       <c r="I68" t="n">
         <v>635.3379562382198</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.37</v>
+        <v>-13.87</v>
       </c>
       <c r="L68" t="n">
-        <v>8.109999999999999</v>
+        <v>14.84</v>
       </c>
       <c r="M68" t="n">
-        <v>0.89</v>
+        <v>5.96</v>
       </c>
       <c r="N68" t="n">
-        <v>3.84</v>
+        <v>7.02</v>
       </c>
       <c r="O68" t="n">
         <v>1.45</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>13.92</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="H69" t="n">
-        <v>687.05</v>
+        <v>693.75</v>
       </c>
       <c r="I69" t="n">
         <v>691.0560207411356</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>-12.99</v>
+        <v>-14.09</v>
       </c>
       <c r="L69" t="n">
-        <v>14.45</v>
+        <v>14.96</v>
       </c>
       <c r="M69" t="n">
         <v>3.08</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H70" t="n">
-        <v>826.3</v>
+        <v>787.2</v>
       </c>
       <c r="I70" t="n">
         <v>809.6685948446675</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K70" t="n">
-        <v>19.11</v>
+        <v>13.47</v>
       </c>
       <c r="L70" t="n">
         <v>10.93</v>
@@ -4431,7 +5270,7 @@
         <v>2.52</v>
       </c>
       <c r="N70" t="n">
-        <v>3.56</v>
+        <v>4.73</v>
       </c>
       <c r="O70" t="n">
         <v>0.98</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>9.42</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="H71" t="n">
-        <v>756.3</v>
+        <v>769.7</v>
       </c>
       <c r="I71" t="n">
         <v>762.9326588426322</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K71" t="n">
-        <v>3.93</v>
+        <v>2.22</v>
       </c>
       <c r="L71" t="n">
         <v>4.22</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.49</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H72" t="n">
-        <v>741.1</v>
+        <v>725.35</v>
       </c>
       <c r="I72" t="n">
         <v>740.9243247295909</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.72</v>
+        <v>-5.76</v>
       </c>
       <c r="L72" t="n">
-        <v>4.04</v>
+        <v>6.3</v>
       </c>
       <c r="M72" t="n">
         <v>2.52</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H73" t="n">
-        <v>659.85</v>
+        <v>661.3</v>
       </c>
       <c r="I73" t="n">
         <v>660.4754559904637</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K73" t="n">
-        <v>9.029999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="L73" t="n">
         <v>2</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>11.59</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="H74" t="n">
-        <v>610.8</v>
+        <v>603.85</v>
       </c>
       <c r="I74" t="n">
         <v>610.6436147923072</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.64</v>
+        <v>-8.69</v>
       </c>
       <c r="L74" t="n">
-        <v>8.5</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M74" t="n">
         <v>1.56</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H75" t="n">
-        <v>534.1</v>
+        <v>572.85</v>
       </c>
       <c r="I75" t="n">
         <v>571.3577938854569</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K75" t="n">
-        <v>11.55</v>
+        <v>5.13</v>
       </c>
       <c r="L75" t="n">
         <v>1.52</v>
       </c>
       <c r="M75" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="N75" t="n">
-        <v>3.29</v>
+        <v>7.26</v>
       </c>
       <c r="O75" t="n">
         <v>-1.14</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>13.42</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H76" t="n">
-        <v>577.7</v>
+        <v>561.3</v>
       </c>
       <c r="I76" t="n">
         <v>564.0696841892836</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K76" t="n">
-        <v>0.85</v>
+        <v>-2.02</v>
       </c>
       <c r="L76" t="n">
         <v>4.69</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>9.75</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H77" t="n">
-        <v>587.05</v>
+        <v>614.45</v>
       </c>
       <c r="I77" t="n">
         <v>608.7522885911766</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.59</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>4.97</v>
+        <v>10.51</v>
       </c>
       <c r="M77" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="N77" t="n">
-        <v>4.27</v>
+        <v>4.67</v>
       </c>
       <c r="O77" t="n">
         <v>-2.84</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H78" t="n">
-        <v>644.5</v>
+        <v>620.85</v>
       </c>
       <c r="I78" t="n">
         <v>638.6169823137352</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K78" t="n">
-        <v>4.89</v>
+        <v>1.04</v>
       </c>
       <c r="L78" t="n">
         <v>2.63</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.66</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H79" t="n">
-        <v>669.5</v>
+        <v>675</v>
       </c>
       <c r="I79" t="n">
         <v>672.6600720122412</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.84</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>8.220000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="M79" t="n">
         <v>0.27</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5004,6 +5963,14 @@
       <c r="Q80" t="n">
         <v>24</v>
       </c>
+      <c r="R80" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9962,7 +10929,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.1</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="6">
@@ -9972,7 +10939,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -9982,7 +10949,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
@@ -9992,7 +10959,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10002,7 +10969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.8</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="10">
@@ -10012,7 +10979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -10022,7 +10989,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -10032,7 +10999,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10042,7 +11009,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.8</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="14">
@@ -10052,7 +11019,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.33</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="15">
@@ -10062,7 +11029,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.16</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -10072,7 +11039,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="17">
@@ -10082,7 +11049,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65.06999999999999</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="18">
@@ -10092,7 +11059,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="19">
@@ -10102,7 +11069,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.34</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="20">
@@ -10112,7 +11079,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.48</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="21">
@@ -10122,7 +11089,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38.39</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="22">
@@ -10132,7 +11099,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -10142,7 +11109,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -10152,7 +11119,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="25">
@@ -10162,7 +11129,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.99</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="26">
@@ -10172,7 +11139,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -10192,7 +11159,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
